--- a/docs/perechen-otchetov/obrazcy/ФО-28.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-28.xlsx
@@ -3523,7 +3523,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="35" t="inlineStr">
         <is>
           <t>1.</t>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B37" s="36" t="inlineStr">
         <is>
-          <t>ИТОГО на 01.10.2026: 21 заёмщик, 24 кредита; остаток основного долга 75 037,500 тыс. сом = ФО-25 = ФО-24 на конец сентября = ИТОГО ФО-02 «по основной сумме» 67 729,500 + КЗ-25 7 308,000 (в образце ФО-02 его нет).</t>
+          <t>ИТОГО на 01.10.2026: 21 заёмщик, 24 кредита; остаток основного долга 75 037,500 тыс. сом = ФО-25 = ФО-24 на конец сентября = ИТОГО ФО-02 «по основной сумме» (в том числе КЗ-25 7 308,000).</t>
         </is>
       </c>
     </row>
